--- a/output/supplementary/Table3_cross_jurisdictional.xlsx
+++ b/output/supplementary/Table3_cross_jurisdictional.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>PCCP framework</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Key sources</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,27 +461,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No (encouraged)</t>
+          <t>Partial / encouraged</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Recommended, not mandatory</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Recommended for generalizability</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>510(k) allowed</t>
+          <t>510(k) pathway allowed</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yes (2023)</t>
+          <t>Yes (final guidance 2023)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FDA PCCP Guidance (2023); FDA/Health Canada/MHRA GMLP principles</t>
         </is>
       </c>
     </row>
@@ -488,12 +498,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Partial (2026)</t>
+          <t>Yes (2026 MLMD guidance)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Partial-to-Yes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +518,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Proposed / evolving</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Health Canada Pre-market Guidance for Machine Learning-enabled Medical Devices (2026)</t>
         </is>
       </c>
     </row>
@@ -520,7 +535,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yes (high-risk)</t>
+          <t>Yes (high-risk systems)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -530,7 +545,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>Effectively expected via representativeness requirements</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -540,7 +555,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lifecycle monitoring</t>
+          <t>Lifecycle monitoring + post-market surveillance</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>EU AI Act Article 10 (Data and data governance)</t>
         </is>
       </c>
     </row>
@@ -552,27 +572,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Limited</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not explicitly required</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not explicitly required</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Similar to FDA</t>
+          <t>Comparable to FDA approach</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under review</t>
+          <t>Under review / IMDRF-aligned</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TGA AI-enabled medical device guidance; IMDRF SaMD framework</t>
         </is>
       </c>
     </row>
@@ -589,12 +614,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Limited</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not explicitly required</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -604,7 +629,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pilot (2024)</t>
+          <t>Pilot discussions (2024 onward)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PMDA AI/ML medical device discussions; IMDRF SaMD principles</t>
         </is>
       </c>
     </row>
